--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_GRISHU-CSTD-0-00-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_GRISHU-CSTD-0-00-A-C0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_mcu\19epfv3_mcu_app_mainline\src\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A8106F-E6CB-4F15-93A3-2140F07C399C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316D7FDA-1DB2-44C4-B931-9BAA35ACE1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7575" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="288">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2769,9 +2769,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>○</t>
-  </si>
-  <si>
     <t>MET-M_REMWAR-CSTD-1-03-B-C0.xlsx</t>
   </si>
   <si>
@@ -3083,6 +3080,29 @@
     <t>品質総点検(R4)：Alert設計書の修正対応
 [B_GRISHU]シート
 ・数式の変更(AU10、AU11)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>－</t>
+  </si>
+  <si>
+    <t>BEVリベース(シス検追従)対応
+[Matrix]シート
+・RWの削除</t>
+    <rPh sb="33" eb="35">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1.1.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DT廣瀬冴</t>
+    <rPh sb="0" eb="5">
+      <t>dtヒロセサエ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5248,6 +5268,9 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5272,9 +5295,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5287,37 +5307,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5362,10 +5361,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -9974,6 +9994,7 @@
       <sheetName val="選定一覧"/>
       <sheetName val="材料受差"/>
       <sheetName val="入力リスト"/>
+      <sheetName val="字段定义"/>
       <sheetName val="議事・勧告一覧"/>
       <sheetName val="rom map"/>
       <sheetName val="前提書情報"/>
@@ -9981,7 +10002,6 @@
       <sheetName val="DataList"/>
       <sheetName val="Cover"/>
       <sheetName val="メニュー画面"/>
-      <sheetName val="字段定义"/>
       <sheetName val="投資ﾌｫﾛｰ"/>
       <sheetName val="説明"/>
       <sheetName val="祝日"/>
@@ -9998,6 +10018,37 @@
       <sheetName val="改訂履歴"/>
       <sheetName val="Sheet1"/>
       <sheetName val="⑥フューエル"/>
+      <sheetName val="STEP1-Definition"/>
+      <sheetName val="No.31"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="测试计划"/>
+      <sheetName val="2.2.4_起動終了時"/>
+      <sheetName val="全戻りﾊﾞｸﾞ"/>
+      <sheetName val="DataShare"/>
+      <sheetName val="ＯＰＭ設備"/>
+      <sheetName val="償却計算"/>
+      <sheetName val="技術費"/>
+      <sheetName val="消耗材"/>
+      <sheetName val="生産用消耗工具費"/>
+      <sheetName val="投資込みＭＪ原価"/>
+      <sheetName val="ＭＪ加工費"/>
+      <sheetName val="仕損根拠"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="調査シート"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="SCH"/>
+      <sheetName val="发行控制"/>
+      <sheetName val="Vibrate test"/>
+      <sheetName val="Data"/>
+      <sheetName val="注釈"/>
+      <sheetName val="仕向け決定用情報取得(GM250)"/>
+      <sheetName val="付録①（GM用）"/>
+      <sheetName val="Data.Share"/>
+      <sheetName val="Func.Share"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -10120,6 +10171,37 @@
       <sheetData sheetId="99" refreshError="1"/>
       <sheetData sheetId="100" refreshError="1"/>
       <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10246,24 +10328,61 @@
       <sheetName val="県別ﾏﾙﾁ"/>
       <sheetName val="車両仕様"/>
       <sheetName val="FMEA記載方法"/>
-      <sheetName val="基本情報"/>
-      <sheetName val="リスク"/>
+      <sheetName val="STEP1-Definition"/>
       <sheetName val="改訂履歴"/>
-      <sheetName val="ソフト開発"/>
-      <sheetName val="開発範囲・規約"/>
-      <sheetName val="品質"/>
-      <sheetName val="開発日程"/>
-      <sheetName val="STEP1-Definition"/>
       <sheetName val="ListWork"/>
       <sheetName val="Config - dspmgr"/>
       <sheetName val="凡例・注記記載用"/>
       <sheetName val="入力パラメータ"/>
       <sheetName val="原紙"/>
+      <sheetName val="基本情報"/>
+      <sheetName val="リスク"/>
+      <sheetName val="ソフト開発"/>
+      <sheetName val="開発範囲・規約"/>
+      <sheetName val="品質"/>
+      <sheetName val="開発日程"/>
       <sheetName val="マスタテーブル登録データ"/>
       <sheetName val="記入シート"/>
       <sheetName val="format"/>
       <sheetName val="検査シート"/>
       <sheetName val="1.概述"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="集計表"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="Defined Layout Screen_Ver.0.6"/>
+      <sheetName val="ｲﾝﾊﾟｸﾄ影響台数集計表"/>
+      <sheetName val="実勢(売上)台数表"/>
+      <sheetName val="月別企画台数表"/>
+      <sheetName val="プロジェクト一覧表(現行)"/>
+      <sheetName val="限界利益表(半期別)"/>
+      <sheetName val="機種マスタ"/>
+      <sheetName val="機種ﾏｽﾀ（他車）"/>
+      <sheetName val="売上高表(半期別)"/>
+      <sheetName val="地点情報データ応答"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="リソーセス算出"/>
+      <sheetName val="定義"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="変更区分一覧"/>
+      <sheetName val="難易度量一覧"/>
+      <sheetName val="ユーザ一覧"/>
+      <sheetName val="Normal(Mark)"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="入力規則"/>
+      <sheetName val="#REF"/>
+      <sheetName val="Contents"/>
+      <sheetName val="選択肢"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -10407,6 +10526,43 @@
       <sheetData sheetId="132" refreshError="1"/>
       <sheetData sheetId="133" refreshError="1"/>
       <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
+      <sheetData sheetId="153" refreshError="1"/>
+      <sheetData sheetId="154" refreshError="1"/>
+      <sheetData sheetId="155" refreshError="1"/>
+      <sheetData sheetId="156" refreshError="1"/>
+      <sheetData sheetId="157" refreshError="1"/>
+      <sheetData sheetId="158" refreshError="1"/>
+      <sheetData sheetId="159" refreshError="1"/>
+      <sheetData sheetId="160" refreshError="1"/>
+      <sheetData sheetId="161" refreshError="1"/>
+      <sheetData sheetId="162" refreshError="1"/>
+      <sheetData sheetId="163" refreshError="1"/>
+      <sheetData sheetId="164" refreshError="1"/>
+      <sheetData sheetId="165" refreshError="1"/>
+      <sheetData sheetId="166" refreshError="1"/>
+      <sheetData sheetId="167" refreshError="1"/>
+      <sheetData sheetId="168" refreshError="1"/>
+      <sheetData sheetId="169" refreshError="1"/>
+      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="171" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10588,10 +10744,10 @@
       <sheetName val="CPF"/>
       <sheetName val="編集"/>
       <sheetName val="PAIData"/>
+      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="NCastalone"/>
       <sheetName val="dongia (2)"/>
       <sheetName val="Volumes"/>
-      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="加工費"/>
       <sheetName val="車両仕様 嗼1嗼1噌1鲌"/>
       <sheetName val="車両仕様 勜+勜+匬+鲌"/>
@@ -10601,8 +10757,8 @@
       <sheetName val="Y230"/>
       <sheetName val="MASTER"/>
       <sheetName val="設定"/>
+      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="⑥フューエル"/>
-      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ"/>
       <sheetName val="設品表01-3-23作成"/>
       <sheetName val="wire"/>
@@ -10618,25 +10774,24 @@
       <sheetName val="610L611L品番一覧"/>
       <sheetName val="【Input】見積基礎情報（海外生産分)"/>
       <sheetName val="IM-P-L-JB "/>
-      <sheetName val="797T輸入部品リスト"/>
-      <sheetName val="テーブル"/>
-      <sheetName val="Master Updated(517)"/>
-      <sheetName val="４-２．151項目累積（日本）"/>
-      <sheetName val="５-２．151項目累積（北米）"/>
-      <sheetName val="５-１．151項目詳細（北米）"/>
-      <sheetName val="545N仕様ﾗﾌ2"/>
-      <sheetName val="商品力向上"/>
-      <sheetName val="OP-PD"/>
-      <sheetName val="６２３Ｔ"/>
+      <sheetName val="RMBSS's Triggered"/>
+      <sheetName val="_"/>
       <sheetName val="Main 2"/>
       <sheetName val="Datasheet from R. Hinds"/>
-      <sheetName val="GMT900 IPC"/>
+      <sheetName val="545N仕様ﾗﾌ2"/>
+      <sheetName val="Master Updated(517)"/>
+      <sheetName val="６２３Ｔ"/>
+      <sheetName val="商品力向上"/>
+      <sheetName val="ED AND EDOV"/>
       <sheetName val="HORAS_TRAB"/>
       <sheetName val="Resumo_Corolla"/>
       <sheetName val="GASTOS_COROLLA"/>
-      <sheetName val="CALC"/>
-      <sheetName val="ﾘｽﾄ候補"/>
-      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="④要素記号一覧表"/>
+      <sheetName val="START"/>
+      <sheetName val="Blue Flag"/>
+      <sheetName val="Calc Sheet Budget"/>
+      <sheetName val="見積一覧（１案）"/>
+      <sheetName val="部品"/>
       <sheetName val="①評価項目_メーカー"/>
       <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0011__x00"/>
       <sheetName val="車両仕様4__x005f_x0000__x005f_x0011__x005f_x0000_"/>
@@ -10663,16 +10818,9 @@
       <sheetName val="車両仕様_4___x005f_x005f_x005f_x005f_x005f_x005f_x001"/>
       <sheetName val="車両仕様4___x005f_x005f_x005f_x005f_x005f_x005f_x0011"/>
       <sheetName val="EFFY_MAZDA"/>
-      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
-      <sheetName val="_"/>
-      <sheetName val="RMBSS's Triggered"/>
-      <sheetName val="ED AND EDOV"/>
-      <sheetName val="④要素記号一覧表"/>
-      <sheetName val="START"/>
-      <sheetName val="Blue Flag"/>
-      <sheetName val="Calc Sheet Budget"/>
-      <sheetName val="見積一覧（１案）"/>
-      <sheetName val="部品"/>
+      <sheetName val="４-２．151項目累積（日本）"/>
+      <sheetName val="５-２．151項目累積（北米）"/>
+      <sheetName val="５-１．151項目詳細（北米）"/>
       <sheetName val="sebelumCR"/>
       <sheetName val="08TMME"/>
       <sheetName val="VCPT"/>
@@ -10682,6 +10830,14 @@
       <sheetName val="WIP Cal Sheet"/>
       <sheetName val="Pricing overview"/>
       <sheetName val="駆動系1"/>
+      <sheetName val="797T輸入部品リスト"/>
+      <sheetName val="テーブル"/>
+      <sheetName val="OP-PD"/>
+      <sheetName val="GMT900 IPC"/>
+      <sheetName val="CALC"/>
+      <sheetName val="ﾘｽﾄ候補"/>
+      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
       <sheetName val="393.N"/>
       <sheetName val="CæÊ _x0015_ Op"/>
       <sheetName val="ƒƒCƒ“‰æ–Ê _x0015_ Op"/>
@@ -10701,6 +10857,10 @@
       <sheetName val="車両仕様_ᵣ逰ᵣ邀ᵣ郰ᵣ"/>
       <sheetName val="他"/>
       <sheetName val="part"/>
+      <sheetName val="415T原"/>
+      <sheetName val="PAC14"/>
+      <sheetName val="部品表"/>
+      <sheetName val="■07中期明細雛形"/>
       <sheetName val="Vectra"/>
       <sheetName val="PRADO"/>
       <sheetName val="Previous"/>
@@ -10740,10 +10900,6 @@
       <sheetName val="OTHERS x620"/>
       <sheetName val="Ref"/>
       <sheetName val="TOTAL P2"/>
-      <sheetName val="415T原"/>
-      <sheetName val="PAC14"/>
-      <sheetName val="部品表"/>
-      <sheetName val="■07中期明細雛形"/>
       <sheetName val="BUYERS"/>
       <sheetName val="Status"/>
       <sheetName val="PR"/>
@@ -11731,7 +11887,6 @@
       <sheetName val="SUM"/>
       <sheetName val="ﾄﾗｯｸ"/>
       <sheetName val="00"/>
-      <sheetName val="課題管理"/>
       <sheetName val="C-55227AB"/>
       <sheetName val="Data Definition"/>
       <sheetName val="FC_まとめる"/>
@@ -11741,6 +11896,7 @@
       <sheetName val="RGB"/>
       <sheetName val="車両仕様_4___x0011__x00"/>
       <sheetName val="ドメインリスト"/>
+      <sheetName val="課題管理"/>
       <sheetName val="option"/>
       <sheetName val="追加検討（調光外部出力）"/>
       <sheetName val="入力規則"/>
@@ -11833,8 +11989,15 @@
       <sheetName val="入力LIST"/>
       <sheetName val="パラメータ一覧(AXSS.AXCS)"/>
       <sheetName val="設定値定義"/>
+      <sheetName val="集計表"/>
+      <sheetName val="format"/>
+      <sheetName val="Ｓｉ問連"/>
+      <sheetName val="アップロード系(2)"/>
       <sheetName val="車両仕様????帅?"/>
       <sheetName val="Net Price Position _ Sheet 1"/>
+      <sheetName val="エンジン型式"/>
+      <sheetName val="MET397D-25"/>
+      <sheetName val="要求仕様Ｑ＆Ａ-ソフト"/>
       <sheetName val="POs"/>
       <sheetName val="計算式"/>
       <sheetName val="工管合計"/>
@@ -13368,13 +13531,6 @@
       <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
       <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
       <sheetName val="台数"/>
-      <sheetName val="MET397D-25"/>
-      <sheetName val="集計表"/>
-      <sheetName val="format"/>
-      <sheetName val="要求仕様Ｑ＆Ａ-ソフト"/>
-      <sheetName val="Ｓｉ問連"/>
-      <sheetName val="アップロード系(2)"/>
-      <sheetName val="エンジン型式"/>
       <sheetName val="リストデータ"/>
       <sheetName val="All"/>
       <sheetName val="58831-06360"/>
@@ -13401,6 +13557,185 @@
       <sheetName val="config"/>
       <sheetName val="地点情報データ応答"/>
       <sheetName val="Par"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="ETC機能判定"/>
+      <sheetName val="ETCメニュー"/>
+      <sheetName val="登録情報表示"/>
+      <sheetName val="ETC設定"/>
+      <sheetName val="履歴情報表示"/>
+      <sheetName val="履歴情報詳細表示"/>
+      <sheetName val="メニュー２"/>
+      <sheetName val="割込み(Disp)"/>
+      <sheetName val="割込み(Navi)"/>
+      <sheetName val="走行強制状態変化"/>
+      <sheetName val="入力パラメータ"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="リスト画面"/>
+      <sheetName val="特殊画面"/>
+      <sheetName val="入力画面"/>
+      <sheetName val="メッセージ受信開始"/>
+      <sheetName val="Mark"/>
+      <sheetName val="Contents"/>
+      <sheetName val="車両仕様4_ "/>
+      <sheetName val="改正履歴"/>
+      <sheetName val="リスト選択用"/>
+      <sheetName val="变更履历"/>
+      <sheetName val="Menu List"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="検査シート"/>
+      <sheetName val="Cover"/>
+      <sheetName val="MIS REPORT "/>
+      <sheetName val="（別紙5-1）PP02簡素化"/>
+      <sheetName val="universal"/>
+      <sheetName val="Cost Casting"/>
+      <sheetName val="paint mtrl"/>
+      <sheetName val="corolla_095W_"/>
+      <sheetName val="dyna"/>
+      <sheetName val="FC"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="ﾕｰｻﾞｰ設定"/>
+      <sheetName val="同行评审"/>
+      <sheetName val="5.心配点抽出-0"/>
+      <sheetName val="0.表紙"/>
+      <sheetName val="1._概要"/>
+      <sheetName val="4 選局"/>
+      <sheetName val="定数"/>
+      <sheetName val="Case 21_1"/>
+      <sheetName val="96期(川崎)"/>
+      <sheetName val="ORDSHP"/>
+      <sheetName val="B"/>
+      <sheetName val="Blue_Flag3"/>
+      <sheetName val="Calc_Sheet_Budget3"/>
+      <sheetName val="_PART_479W_LHD3"/>
+      <sheetName val="_PART_MYY5A3"/>
+      <sheetName val="393_N3"/>
+      <sheetName val="WIP_Cal_Sheet3"/>
+      <sheetName val="Pricing_overview3"/>
+      <sheetName val="Lookup_Table3"/>
+      <sheetName val="promo_lists_20113"/>
+      <sheetName val="車両仕様_嗼1嗼1噌1鲌3"/>
+      <sheetName val="車両仕様_勜+勜+匬+鲌3"/>
+      <sheetName val="EquipmentTrimming_Cabin_NS3"/>
+      <sheetName val="Reference_3"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000_?_x005f_x0012_?瞳?3"/>
+      <sheetName val="車両仕様_???_x005f_x0012_?瞳?3"/>
+      <sheetName val="160th_NPCC_Nov'103"/>
+      <sheetName val="RMBSS's_Triggered3"/>
+      <sheetName val="車両仕様?4???_??3"/>
+      <sheetName val="車両仕様_???_?瞳?3"/>
+      <sheetName val="車両仕様???ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様?4??_?3"/>
+      <sheetName val="車両仕様4??_?3"/>
+      <sheetName val="車両仕様____瞳_3"/>
+      <sheetName val="車両仕様______瞳_3"/>
+      <sheetName val="車両仕様_4______3"/>
+      <sheetName val="車両仕様___ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様_4____3"/>
+      <sheetName val="車両仕様4____3"/>
+      <sheetName val="PRICE_LIST3"/>
+      <sheetName val="Loss_Time3"/>
+      <sheetName val="Price_range_IT3"/>
+      <sheetName val="Avensis+d_seg__in_&amp;_out_of_UK+3"/>
+      <sheetName val="#ofclose__xl3"/>
+      <sheetName val="Annexes_toutes_bases3"/>
+      <sheetName val="DON_GIA3"/>
+      <sheetName val="CHITIET_VL-NC3"/>
+      <sheetName val="TONGKE3p_3"/>
+      <sheetName val="TOTAL_P23"/>
+      <sheetName val="2_-_Summary3"/>
+      <sheetName val="IPOTESI_PIANO_STATICA3"/>
+      <sheetName val="make_up3"/>
+      <sheetName val="車両仕様_???_x005f_x005f_x005f_x0012_?瞳?3"/>
+      <sheetName val="調達担当者(06_2～)3"/>
+      <sheetName val="車両仕様__x005f_x0000__2"/>
+      <sheetName val="車両仕様_x005f_x0000__N2"/>
+      <sheetName val="車両仕様___x005f_x0012_2"/>
+      <sheetName val="車両仕様__x005f_x005f_x2"/>
+      <sheetName val="車両仕様___x005f_x005f_2"/>
+      <sheetName val="05-065_she2"/>
+      <sheetName val="idgr_-_formula2"/>
+      <sheetName val="IDGR_(3)2"/>
+      <sheetName val="IDGR_(2)2"/>
+      <sheetName val="PLIV_(3)2"/>
+      <sheetName val="PLIV_(2)2"/>
+      <sheetName val="PLIV_(template)2"/>
+      <sheetName val="inv_recon2"/>
+      <sheetName val="side_member2"/>
+      <sheetName val="TTC_(FG)2"/>
+      <sheetName val="Sheet1_(3)2"/>
+      <sheetName val="truck_allocation2"/>
+      <sheetName val="Supplier_Price_Check2"/>
+      <sheetName val="$_-_june2"/>
+      <sheetName val="Vios_Cost_Reduction_actual_pro2"/>
+      <sheetName val="RET_PALLET2"/>
+      <sheetName val="Form_A2"/>
+      <sheetName val="NG_SUMMARY2"/>
+      <sheetName val="impact_pallet_and_racks2"/>
+      <sheetName val="Daily_WSD2"/>
+      <sheetName val="ass'y_12'04-05'053"/>
+      <sheetName val="Type_I2"/>
+      <sheetName val="Schedule_PM2"/>
+      <sheetName val="training_forklift2"/>
+      <sheetName val="Budget_by_Category2"/>
+      <sheetName val="investment_tmc_v8_0_34p2"/>
+      <sheetName val="PTD_Activity2"/>
+      <sheetName val="Sample_1PP_2"/>
+      <sheetName val="Open_Ran3"/>
+      <sheetName val="Open_RAN_23"/>
+      <sheetName val="CHIA_KH2"/>
+      <sheetName val="Purch__BP2"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0013"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0053"/>
+      <sheetName val="ＰＲＥ_NO1"/>
+      <sheetName val="Courier_4x2"/>
+      <sheetName val="Price_Trend2"/>
+      <sheetName val="車両仕様_?_x005f_x0012_?瞳?2"/>
+      <sheetName val="YARIS_HB2"/>
+      <sheetName val="00_KS"/>
+      <sheetName val="PRADO_3Dr_fl2"/>
+      <sheetName val="01_DATA2"/>
+      <sheetName val="Quality_Update2"/>
+      <sheetName val="prior_data"/>
+      <sheetName val="Table_Master"/>
+      <sheetName val="1_概述"/>
+      <sheetName val="Drop-down_Menu_List"/>
+      <sheetName val="Open_Item_List"/>
+      <sheetName val="本修正_DIFF_"/>
+      <sheetName val="Sector_Assignment"/>
+      <sheetName val="BQ_CONVEYOR"/>
+      <sheetName val="IMV_LIST_2003"/>
+      <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0000___x0"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000____瞳_"/>
+      <sheetName val="Part_list"/>
+      <sheetName val="INACT797"/>
+      <sheetName val="M1A"/>
+      <sheetName val="OK"/>
+      <sheetName val="??? Pilling upu_S y"/>
+      <sheetName val="ASF INVENTORY"/>
+      <sheetName val="車両仕様_4___x005f_x0013__x0013__x0013__x0013__x0013_"/>
+      <sheetName val="ጀጀ؀ԀЀࠀ᐀Ѐऀ܀̀܀ഀ܀Ԁऀ଀ࠀ_x0000_"/>
+      <sheetName val="CTable"/>
+      <sheetName val="bs is"/>
+      <sheetName val="成績"/>
+      <sheetName val="IT Checklist"/>
+      <sheetName val="コマンド認識, DTMF"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="BEEP設定"/>
+      <sheetName val="標準仕様DB"/>
+      <sheetName val="No.31"/>
+      <sheetName val="CS2_SmcDriverインテグ項目"/>
+      <sheetName val="休日"/>
+      <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
+      <sheetName val="5．キー入力動作説明"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="試験項目_R3小"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -13890,33 +14225,45 @@
       <sheetData sheetId="304" refreshError="1"/>
       <sheetData sheetId="305" refreshError="1"/>
       <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307">
+      <sheetData sheetId="307" refreshError="1"/>
+      <sheetData sheetId="308" refreshError="1"/>
+      <sheetData sheetId="309" refreshError="1"/>
+      <sheetData sheetId="310" refreshError="1"/>
+      <sheetData sheetId="311">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="308">
+      <sheetData sheetId="312">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="309">
+      <sheetData sheetId="313">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="310"/>
-      <sheetData sheetId="311"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
+      <sheetData sheetId="314">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="315">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="316" refreshError="1"/>
       <sheetData sheetId="317" refreshError="1"/>
       <sheetData sheetId="318" refreshError="1"/>
@@ -15488,8 +15835,8 @@
       </sheetData>
       <sheetData sheetId="793">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>1</v>
+          <cell r="A1" t="str">
+            <v>ﾄﾖﾀ自動車株式会社　調達本部　</v>
           </cell>
         </row>
       </sheetData>
@@ -15525,7 +15872,13 @@
       <sheetData sheetId="805" refreshError="1"/>
       <sheetData sheetId="806" refreshError="1"/>
       <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808"/>
+      <sheetData sheetId="808">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="809" refreshError="1"/>
       <sheetData sheetId="810" refreshError="1"/>
       <sheetData sheetId="811" refreshError="1"/>
@@ -16488,9 +16841,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1050">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16712,9 +17065,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1082">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16733,9 +17086,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1085">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17062,9 +17415,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1132">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17153,9 +17506,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1145">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17384,16 +17737,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1178">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1179">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17433,9 +17786,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1185">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17461,9 +17814,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1189">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17482,9 +17835,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1192">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17552,9 +17905,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1202">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17573,16 +17926,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1205">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1206">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17594,16 +17947,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1208">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1209">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17643,9 +17996,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1215">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17671,9 +18024,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1219">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17692,9 +18045,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1222">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17762,9 +18115,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1232">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17783,16 +18136,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1235">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1236">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17804,16 +18157,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1238">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1239">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17853,16 +18206,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1245">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1246">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17922,16 +18275,76 @@
       <sheetData sheetId="1294"/>
       <sheetData sheetId="1295" refreshError="1"/>
       <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297"/>
-      <sheetData sheetId="1298"/>
-      <sheetData sheetId="1299"/>
-      <sheetData sheetId="1300"/>
-      <sheetData sheetId="1301"/>
-      <sheetData sheetId="1302"/>
-      <sheetData sheetId="1303"/>
-      <sheetData sheetId="1304"/>
-      <sheetData sheetId="1305"/>
-      <sheetData sheetId="1306"/>
+      <sheetData sheetId="1297">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1298">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1299">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1300">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1301">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1302">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1303">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1304">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1305">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1306">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1307" refreshError="1"/>
       <sheetData sheetId="1308" refreshError="1"/>
       <sheetData sheetId="1309" refreshError="1"/>
@@ -17940,8 +18353,8 @@
       <sheetData sheetId="1312" refreshError="1"/>
       <sheetData sheetId="1313" refreshError="1"/>
       <sheetData sheetId="1314" refreshError="1"/>
-      <sheetData sheetId="1315" refreshError="1"/>
-      <sheetData sheetId="1316"/>
+      <sheetData sheetId="1315"/>
+      <sheetData sheetId="1316" refreshError="1"/>
       <sheetData sheetId="1317" refreshError="1"/>
       <sheetData sheetId="1318" refreshError="1"/>
       <sheetData sheetId="1319" refreshError="1"/>
@@ -18042,38 +18455,38 @@
       <sheetData sheetId="1414" refreshError="1"/>
       <sheetData sheetId="1415" refreshError="1"/>
       <sheetData sheetId="1416" refreshError="1"/>
-      <sheetData sheetId="1417"/>
+      <sheetData sheetId="1417" refreshError="1"/>
       <sheetData sheetId="1418" refreshError="1"/>
       <sheetData sheetId="1419" refreshError="1"/>
       <sheetData sheetId="1420" refreshError="1"/>
-      <sheetData sheetId="1421" refreshError="1"/>
+      <sheetData sheetId="1421"/>
       <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423"/>
-      <sheetData sheetId="1424"/>
-      <sheetData sheetId="1425"/>
-      <sheetData sheetId="1426"/>
-      <sheetData sheetId="1427"/>
-      <sheetData sheetId="1428"/>
-      <sheetData sheetId="1429"/>
+      <sheetData sheetId="1423" refreshError="1"/>
+      <sheetData sheetId="1424" refreshError="1"/>
+      <sheetData sheetId="1425" refreshError="1"/>
+      <sheetData sheetId="1426" refreshError="1"/>
+      <sheetData sheetId="1427" refreshError="1"/>
+      <sheetData sheetId="1428" refreshError="1"/>
+      <sheetData sheetId="1429" refreshError="1"/>
       <sheetData sheetId="1430"/>
       <sheetData sheetId="1431"/>
       <sheetData sheetId="1432"/>
       <sheetData sheetId="1433"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435">
-        <row r="3">
-          <cell r="C3" t="str">
-            <v>2022年</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1434"/>
+      <sheetData sheetId="1435"/>
       <sheetData sheetId="1436"/>
       <sheetData sheetId="1437"/>
       <sheetData sheetId="1438"/>
       <sheetData sheetId="1439"/>
       <sheetData sheetId="1440"/>
-      <sheetData sheetId="1441"/>
-      <sheetData sheetId="1442"/>
+      <sheetData sheetId="1441" refreshError="1"/>
+      <sheetData sheetId="1442">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>2022年</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1443"/>
       <sheetData sheetId="1444"/>
       <sheetData sheetId="1445"/>
@@ -18153,19 +18566,73 @@
       <sheetData sheetId="1519"/>
       <sheetData sheetId="1520"/>
       <sheetData sheetId="1521"/>
-      <sheetData sheetId="1522"/>
-      <sheetData sheetId="1523"/>
+      <sheetData sheetId="1522">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1523">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1524"/>
-      <sheetData sheetId="1525"/>
+      <sheetData sheetId="1525">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1526"/>
-      <sheetData sheetId="1527"/>
-      <sheetData sheetId="1528"/>
-      <sheetData sheetId="1529"/>
+      <sheetData sheetId="1527">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1528">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1529">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1530"/>
-      <sheetData sheetId="1531"/>
+      <sheetData sheetId="1531">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1532"/>
-      <sheetData sheetId="1533"/>
-      <sheetData sheetId="1534"/>
+      <sheetData sheetId="1533">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1534">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1535"/>
       <sheetData sheetId="1536"/>
       <sheetData sheetId="1537"/>
@@ -19569,30 +20036,30 @@
       <sheetData sheetId="2935"/>
       <sheetData sheetId="2936"/>
       <sheetData sheetId="2937"/>
-      <sheetData sheetId="2938">
-        <row r="1">
-          <cell r="A1"/>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2938"/>
       <sheetData sheetId="2939"/>
       <sheetData sheetId="2940"/>
       <sheetData sheetId="2941"/>
-      <sheetData sheetId="2942" refreshError="1"/>
-      <sheetData sheetId="2943">
+      <sheetData sheetId="2942"/>
+      <sheetData sheetId="2943"/>
+      <sheetData sheetId="2944"/>
+      <sheetData sheetId="2945">
+        <row r="1">
+          <cell r="A1"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2946"/>
+      <sheetData sheetId="2947"/>
+      <sheetData sheetId="2948"/>
+      <sheetData sheetId="2949" refreshError="1"/>
+      <sheetData sheetId="2950">
         <row r="1">
           <cell r="B1" t="str">
             <v>文章管理番号</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2944"/>
-      <sheetData sheetId="2945" refreshError="1"/>
-      <sheetData sheetId="2946" refreshError="1"/>
-      <sheetData sheetId="2947" refreshError="1"/>
-      <sheetData sheetId="2948" refreshError="1"/>
-      <sheetData sheetId="2949" refreshError="1"/>
-      <sheetData sheetId="2950" refreshError="1"/>
-      <sheetData sheetId="2951" refreshError="1"/>
+      <sheetData sheetId="2951"/>
       <sheetData sheetId="2952" refreshError="1"/>
       <sheetData sheetId="2953" refreshError="1"/>
       <sheetData sheetId="2954" refreshError="1"/>
@@ -19626,6 +20093,323 @@
       <sheetData sheetId="2982" refreshError="1"/>
       <sheetData sheetId="2983" refreshError="1"/>
       <sheetData sheetId="2984" refreshError="1"/>
+      <sheetData sheetId="2985" refreshError="1"/>
+      <sheetData sheetId="2986" refreshError="1"/>
+      <sheetData sheetId="2987" refreshError="1"/>
+      <sheetData sheetId="2988" refreshError="1"/>
+      <sheetData sheetId="2989" refreshError="1"/>
+      <sheetData sheetId="2990" refreshError="1"/>
+      <sheetData sheetId="2991" refreshError="1"/>
+      <sheetData sheetId="2992" refreshError="1"/>
+      <sheetData sheetId="2993" refreshError="1"/>
+      <sheetData sheetId="2994" refreshError="1"/>
+      <sheetData sheetId="2995" refreshError="1"/>
+      <sheetData sheetId="2996" refreshError="1"/>
+      <sheetData sheetId="2997" refreshError="1"/>
+      <sheetData sheetId="2998" refreshError="1"/>
+      <sheetData sheetId="2999" refreshError="1"/>
+      <sheetData sheetId="3000" refreshError="1"/>
+      <sheetData sheetId="3001" refreshError="1"/>
+      <sheetData sheetId="3002" refreshError="1"/>
+      <sheetData sheetId="3003" refreshError="1"/>
+      <sheetData sheetId="3004" refreshError="1"/>
+      <sheetData sheetId="3005" refreshError="1"/>
+      <sheetData sheetId="3006" refreshError="1"/>
+      <sheetData sheetId="3007" refreshError="1"/>
+      <sheetData sheetId="3008" refreshError="1"/>
+      <sheetData sheetId="3009" refreshError="1"/>
+      <sheetData sheetId="3010" refreshError="1"/>
+      <sheetData sheetId="3011" refreshError="1"/>
+      <sheetData sheetId="3012" refreshError="1"/>
+      <sheetData sheetId="3013" refreshError="1"/>
+      <sheetData sheetId="3014" refreshError="1"/>
+      <sheetData sheetId="3015" refreshError="1"/>
+      <sheetData sheetId="3016" refreshError="1"/>
+      <sheetData sheetId="3017" refreshError="1"/>
+      <sheetData sheetId="3018" refreshError="1"/>
+      <sheetData sheetId="3019" refreshError="1"/>
+      <sheetData sheetId="3020" refreshError="1"/>
+      <sheetData sheetId="3021" refreshError="1"/>
+      <sheetData sheetId="3022" refreshError="1"/>
+      <sheetData sheetId="3023" refreshError="1"/>
+      <sheetData sheetId="3024" refreshError="1"/>
+      <sheetData sheetId="3025" refreshError="1"/>
+      <sheetData sheetId="3026" refreshError="1"/>
+      <sheetData sheetId="3027" refreshError="1"/>
+      <sheetData sheetId="3028" refreshError="1"/>
+      <sheetData sheetId="3029" refreshError="1"/>
+      <sheetData sheetId="3030" refreshError="1"/>
+      <sheetData sheetId="3031" refreshError="1"/>
+      <sheetData sheetId="3032" refreshError="1"/>
+      <sheetData sheetId="3033" refreshError="1"/>
+      <sheetData sheetId="3034"/>
+      <sheetData sheetId="3035"/>
+      <sheetData sheetId="3036"/>
+      <sheetData sheetId="3037"/>
+      <sheetData sheetId="3038"/>
+      <sheetData sheetId="3039"/>
+      <sheetData sheetId="3040"/>
+      <sheetData sheetId="3041"/>
+      <sheetData sheetId="3042"/>
+      <sheetData sheetId="3043"/>
+      <sheetData sheetId="3044"/>
+      <sheetData sheetId="3045"/>
+      <sheetData sheetId="3046"/>
+      <sheetData sheetId="3047"/>
+      <sheetData sheetId="3048"/>
+      <sheetData sheetId="3049"/>
+      <sheetData sheetId="3050"/>
+      <sheetData sheetId="3051"/>
+      <sheetData sheetId="3052"/>
+      <sheetData sheetId="3053"/>
+      <sheetData sheetId="3054"/>
+      <sheetData sheetId="3055"/>
+      <sheetData sheetId="3056"/>
+      <sheetData sheetId="3057"/>
+      <sheetData sheetId="3058"/>
+      <sheetData sheetId="3059"/>
+      <sheetData sheetId="3060"/>
+      <sheetData sheetId="3061"/>
+      <sheetData sheetId="3062"/>
+      <sheetData sheetId="3063"/>
+      <sheetData sheetId="3064"/>
+      <sheetData sheetId="3065"/>
+      <sheetData sheetId="3066"/>
+      <sheetData sheetId="3067"/>
+      <sheetData sheetId="3068"/>
+      <sheetData sheetId="3069"/>
+      <sheetData sheetId="3070"/>
+      <sheetData sheetId="3071"/>
+      <sheetData sheetId="3072"/>
+      <sheetData sheetId="3073"/>
+      <sheetData sheetId="3074"/>
+      <sheetData sheetId="3075"/>
+      <sheetData sheetId="3076"/>
+      <sheetData sheetId="3077">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3078">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3079">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3080">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3081">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3082">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3083">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3084">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3085">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3086">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3087">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3088">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3089">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3090">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3091">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3092">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3093">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3094">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3095">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3096">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3097">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3098">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3099">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3100"/>
+      <sheetData sheetId="3101"/>
+      <sheetData sheetId="3102"/>
+      <sheetData sheetId="3103"/>
+      <sheetData sheetId="3104"/>
+      <sheetData sheetId="3105"/>
+      <sheetData sheetId="3106"/>
+      <sheetData sheetId="3107"/>
+      <sheetData sheetId="3108"/>
+      <sheetData sheetId="3109"/>
+      <sheetData sheetId="3110"/>
+      <sheetData sheetId="3111"/>
+      <sheetData sheetId="3112"/>
+      <sheetData sheetId="3113"/>
+      <sheetData sheetId="3114"/>
+      <sheetData sheetId="3115"/>
+      <sheetData sheetId="3116"/>
+      <sheetData sheetId="3117"/>
+      <sheetData sheetId="3118"/>
+      <sheetData sheetId="3119"/>
+      <sheetData sheetId="3120"/>
+      <sheetData sheetId="3121"/>
+      <sheetData sheetId="3122"/>
+      <sheetData sheetId="3123"/>
+      <sheetData sheetId="3124"/>
+      <sheetData sheetId="3125"/>
+      <sheetData sheetId="3126"/>
+      <sheetData sheetId="3127"/>
+      <sheetData sheetId="3128"/>
+      <sheetData sheetId="3129"/>
+      <sheetData sheetId="3130"/>
+      <sheetData sheetId="3131"/>
+      <sheetData sheetId="3132"/>
+      <sheetData sheetId="3133"/>
+      <sheetData sheetId="3134"/>
+      <sheetData sheetId="3135"/>
+      <sheetData sheetId="3136"/>
+      <sheetData sheetId="3137" refreshError="1"/>
+      <sheetData sheetId="3138" refreshError="1"/>
+      <sheetData sheetId="3139" refreshError="1"/>
+      <sheetData sheetId="3140" refreshError="1"/>
+      <sheetData sheetId="3141" refreshError="1"/>
+      <sheetData sheetId="3142" refreshError="1"/>
+      <sheetData sheetId="3143" refreshError="1"/>
+      <sheetData sheetId="3144" refreshError="1"/>
+      <sheetData sheetId="3145" refreshError="1"/>
+      <sheetData sheetId="3146" refreshError="1"/>
+      <sheetData sheetId="3147" refreshError="1"/>
+      <sheetData sheetId="3148" refreshError="1"/>
+      <sheetData sheetId="3149" refreshError="1"/>
+      <sheetData sheetId="3150" refreshError="1"/>
+      <sheetData sheetId="3151" refreshError="1"/>
+      <sheetData sheetId="3152" refreshError="1"/>
+      <sheetData sheetId="3153" refreshError="1"/>
+      <sheetData sheetId="3154" refreshError="1"/>
+      <sheetData sheetId="3155" refreshError="1"/>
+      <sheetData sheetId="3156" refreshError="1"/>
+      <sheetData sheetId="3157" refreshError="1"/>
+      <sheetData sheetId="3158" refreshError="1"/>
+      <sheetData sheetId="3159" refreshError="1"/>
+      <sheetData sheetId="3160" refreshError="1"/>
+      <sheetData sheetId="3161" refreshError="1"/>
+      <sheetData sheetId="3162" refreshError="1"/>
+      <sheetData sheetId="3163" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -19731,6 +20515,51 @@
       <sheetName val="入力"/>
       <sheetName val="415T戟L"/>
       <sheetName val="No.31"/>
+      <sheetName val="Navigation"/>
+      <sheetName val="Cover"/>
+      <sheetName val="DataList"/>
+      <sheetName val="変更要件"/>
+      <sheetName val="【石倉編集中】DisplayStateTransitionTa"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="Data"/>
+      <sheetName val="輝度計算(直線用)"/>
+      <sheetName val="コード_dimautocon"/>
+      <sheetName val="パラメータ_dimautocon"/>
+      <sheetName val="パラメータ_dimcalprcnt"/>
+      <sheetName val="パラメータ_dimmanualstep"/>
+      <sheetName val="パラメータ_dimmgr"/>
+      <sheetName val="XX-0080"/>
+      <sheetName val="メッセージ定義"/>
+      <sheetName val="XX-0180"/>
+      <sheetName val="lock"/>
+      <sheetName val="level"/>
+      <sheetName val="cominf"/>
+      <sheetName val="disconnect"/>
+      <sheetName val="★VarUsed"/>
+      <sheetName val="９ｘ"/>
+      <sheetName val="Ｂｘ"/>
+      <sheetName val="Ｃｘ"/>
+      <sheetName val="Ｅｘ"/>
+      <sheetName val="休日"/>
+      <sheetName val="HMI-004_Screen（old）"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="MOTO"/>
+      <sheetName val="前提書情報"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="module"/>
+      <sheetName val="選択肢"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="メニュー"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="R0-10表紙MIC"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="修正ﾌｧｲﾙ一覧"/>
+      <sheetName val="RGB"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -19829,6 +20658,51 @@
       <sheetData sheetId="93" refreshError="1"/>
       <sheetData sheetId="94" refreshError="1"/>
       <sheetData sheetId="95" refreshError="1"/>
+      <sheetData sheetId="96" refreshError="1"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98" refreshError="1"/>
+      <sheetData sheetId="99" refreshError="1"/>
+      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -20187,26 +21061,26 @@
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y34" s="216" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y35" s="235" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z35" s="236"/>
       <c r="AA35" s="236"/>
       <c r="AB35" s="236"/>
       <c r="AC35" s="237"/>
       <c r="AD35" s="235" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AE35" s="236"/>
       <c r="AF35" s="236"/>
       <c r="AG35" s="236"/>
       <c r="AH35" s="237"/>
       <c r="AI35" s="235" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AJ35" s="236"/>
       <c r="AK35" s="236"/>
@@ -20257,21 +21131,21 @@
       <c r="Y38" s="222"/>
       <c r="Z38" s="217"/>
       <c r="AA38" s="218" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AB38" s="217"/>
       <c r="AC38" s="224"/>
       <c r="AD38" s="222"/>
       <c r="AE38" s="217"/>
       <c r="AF38" s="218" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG38" s="217"/>
       <c r="AH38" s="224"/>
       <c r="AI38" s="225"/>
       <c r="AJ38" s="217"/>
       <c r="AK38" s="218" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL38" s="217"/>
       <c r="AM38" s="224"/>
@@ -20306,26 +21180,26 @@
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y42" s="216" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y43" s="235" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z43" s="236"/>
       <c r="AA43" s="236"/>
       <c r="AB43" s="236"/>
       <c r="AC43" s="237"/>
       <c r="AD43" s="235" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AE43" s="236"/>
       <c r="AF43" s="236"/>
       <c r="AG43" s="236"/>
       <c r="AH43" s="237"/>
       <c r="AI43" s="235" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AJ43" s="236"/>
       <c r="AK43" s="236"/>
@@ -20376,21 +21250,21 @@
       <c r="Y46" s="222"/>
       <c r="Z46" s="217"/>
       <c r="AA46" s="218" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AB46" s="217"/>
       <c r="AC46" s="224"/>
       <c r="AD46" s="217"/>
       <c r="AE46" s="217"/>
       <c r="AF46" s="218" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG46" s="217"/>
       <c r="AH46" s="224"/>
       <c r="AI46" s="225"/>
       <c r="AJ46" s="217"/>
       <c r="AK46" s="218" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AL46" s="217"/>
       <c r="AM46" s="224"/>
@@ -20424,26 +21298,26 @@
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
       <c r="Y50" s="216" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
       <c r="Y51" s="235" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z51" s="236"/>
       <c r="AA51" s="236"/>
       <c r="AB51" s="236"/>
       <c r="AC51" s="237"/>
       <c r="AD51" s="235" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AE51" s="236"/>
       <c r="AF51" s="236"/>
       <c r="AG51" s="236"/>
       <c r="AH51" s="237"/>
       <c r="AI51" s="235" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AJ51" s="236"/>
       <c r="AK51" s="236"/>
@@ -20494,21 +21368,21 @@
       <c r="Y54" s="222"/>
       <c r="Z54" s="217"/>
       <c r="AA54" s="218" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AB54" s="217"/>
       <c r="AC54" s="224"/>
       <c r="AD54" s="217"/>
       <c r="AE54" s="217"/>
       <c r="AF54" s="218" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG54" s="217"/>
       <c r="AH54" s="224"/>
       <c r="AI54" s="225"/>
       <c r="AJ54" s="217"/>
       <c r="AK54" s="218" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AL54" s="217"/>
       <c r="AM54" s="224"/>
@@ -20539,7 +21413,7 @@
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
       <c r="AK57" s="213" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -20586,18 +21460,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="246" t="s">
+      <c r="I2" s="238" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="246"/>
-      <c r="K2" s="246"/>
-      <c r="L2" s="246"/>
-      <c r="M2" s="246"/>
-      <c r="N2" s="246"/>
-      <c r="O2" s="246"/>
-      <c r="P2" s="246"/>
-      <c r="Q2" s="246"/>
-      <c r="R2" s="246"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="M2" s="238"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="238"/>
+      <c r="P2" s="238"/>
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -20610,25 +21484,25 @@
       <c r="H3" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I3" s="247" t="s">
+      <c r="I3" s="239" t="s">
         <v>192</v>
       </c>
-      <c r="J3" s="248"/>
-      <c r="K3" s="248"/>
-      <c r="L3" s="248"/>
-      <c r="M3" s="248"/>
-      <c r="N3" s="248"/>
-      <c r="O3" s="248"/>
-      <c r="P3" s="248"/>
-      <c r="Q3" s="248"/>
-      <c r="R3" s="248"/>
+      <c r="J3" s="240"/>
+      <c r="K3" s="240"/>
+      <c r="L3" s="240"/>
+      <c r="M3" s="240"/>
+      <c r="N3" s="240"/>
+      <c r="O3" s="240"/>
+      <c r="P3" s="240"/>
+      <c r="Q3" s="240"/>
+      <c r="R3" s="240"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="21" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.1</v>
+        <v>1.1.0</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -20642,43 +21516,43 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="240" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="241"/>
-      <c r="E7" s="242" t="s">
+      <c r="C7" s="243" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="244"/>
+      <c r="E7" s="245" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="242"/>
-      <c r="G7" s="243" t="s">
+      <c r="F7" s="245"/>
+      <c r="G7" s="246" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="243"/>
-      <c r="I7" s="243"/>
-      <c r="J7" s="243"/>
-      <c r="K7" s="243"/>
-      <c r="L7" s="243"/>
-      <c r="M7" s="244" t="s">
+      <c r="H7" s="246"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="246"/>
+      <c r="K7" s="246"/>
+      <c r="L7" s="246"/>
+      <c r="M7" s="247" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="244"/>
-      <c r="O7" s="244"/>
-      <c r="P7" s="244"/>
-      <c r="Q7" s="244"/>
-      <c r="R7" s="245"/>
-      <c r="S7" s="238" t="s">
-        <v>276</v>
-      </c>
-      <c r="T7" s="238"/>
-      <c r="U7" s="238"/>
-      <c r="V7" s="238"/>
-      <c r="W7" s="238"/>
-      <c r="X7" s="239"/>
+      <c r="N7" s="247"/>
+      <c r="O7" s="247"/>
+      <c r="P7" s="247"/>
+      <c r="Q7" s="247"/>
+      <c r="R7" s="248"/>
+      <c r="S7" s="241" t="s">
+        <v>275</v>
+      </c>
+      <c r="T7" s="241"/>
+      <c r="U7" s="241"/>
+      <c r="V7" s="241"/>
+      <c r="W7" s="241"/>
+      <c r="X7" s="242"/>
     </row>
     <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
@@ -20733,7 +21607,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T8" s="16" t="s">
         <v>7</v>
@@ -20757,34 +21631,34 @@
         <v>1</v>
       </c>
       <c r="C9" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="192" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="192" t="s">
+      <c r="E9" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="G9" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
@@ -20797,22 +21671,22 @@
         <v>44260</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T9" s="231" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="V9" s="231" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="X9" s="232" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="2:24" ht="40.5">
@@ -20821,34 +21695,34 @@
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" s="234" t="s">
         <v>283</v>
       </c>
-      <c r="D10" s="234" t="s">
-        <v>284</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -20861,27 +21735,47 @@
       <c r="U10" s="1"/>
       <c r="V10" s="231"/>
       <c r="W10" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="X10" s="232">
         <v>45806</v>
       </c>
     </row>
-    <row r="11" spans="2:24">
+    <row r="11" spans="2:24" ht="40.5">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D11" s="234" t="s">
+        <v>285</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -20892,8 +21786,12 @@
       <c r="T11" s="231"/>
       <c r="U11" s="1"/>
       <c r="V11" s="231"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="232"/>
+      <c r="W11" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="X11" s="232">
+        <v>45978</v>
+      </c>
     </row>
     <row r="12" spans="2:24">
       <c r="B12" s="9">
@@ -21293,44 +22191,44 @@
   <sheetData>
     <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="278" t="s">
+      <c r="B2" s="253" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="279"/>
-      <c r="D2" s="266" t="s">
+      <c r="C2" s="254"/>
+      <c r="D2" s="259" t="s">
         <v>229</v>
       </c>
-      <c r="E2" s="267"/>
-      <c r="F2" s="267"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="268"/>
+      <c r="E2" s="260"/>
+      <c r="F2" s="260"/>
+      <c r="G2" s="260"/>
+      <c r="H2" s="261"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="253" t="s">
+      <c r="B3" s="255" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="254"/>
-      <c r="D3" s="269" t="s">
+      <c r="C3" s="256"/>
+      <c r="D3" s="262" t="s">
         <v>228</v>
       </c>
-      <c r="E3" s="270"/>
-      <c r="F3" s="270"/>
-      <c r="G3" s="270"/>
-      <c r="H3" s="271"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="263"/>
+      <c r="H3" s="264"/>
     </row>
     <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="264" t="s">
+      <c r="B4" s="257" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="265"/>
-      <c r="D4" s="272" t="str">
+      <c r="C4" s="258"/>
+      <c r="D4" s="265" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_GRISHU-CSTD-0-00-A-C0.c</v>
       </c>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="274"/>
+      <c r="E4" s="266"/>
+      <c r="F4" s="266"/>
+      <c r="G4" s="266"/>
+      <c r="H4" s="267"/>
     </row>
     <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
@@ -21339,70 +22237,70 @@
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="278" t="s">
+      <c r="B6" s="253" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="279"/>
-      <c r="D6" s="275" t="str">
+      <c r="C6" s="254"/>
+      <c r="D6" s="268" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_GRISHU</v>
       </c>
-      <c r="E6" s="276"/>
-      <c r="F6" s="276"/>
-      <c r="G6" s="276"/>
-      <c r="H6" s="277"/>
+      <c r="E6" s="269"/>
+      <c r="F6" s="269"/>
+      <c r="G6" s="269"/>
+      <c r="H6" s="270"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="253" t="s">
+      <c r="B7" s="255" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="254"/>
-      <c r="D7" s="255">
+      <c r="C7" s="256"/>
+      <c r="D7" s="271">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="256"/>
-      <c r="F7" s="256"/>
-      <c r="G7" s="256"/>
-      <c r="H7" s="257"/>
+      <c r="E7" s="272"/>
+      <c r="F7" s="272"/>
+      <c r="G7" s="272"/>
+      <c r="H7" s="273"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="253" t="s">
+      <c r="B8" s="255" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="254"/>
-      <c r="D8" s="255" t="str">
+      <c r="C8" s="256"/>
+      <c r="D8" s="271" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_GRISHU_MTRX</v>
       </c>
-      <c r="E8" s="256"/>
-      <c r="F8" s="256"/>
-      <c r="G8" s="256"/>
-      <c r="H8" s="257"/>
+      <c r="E8" s="272"/>
+      <c r="F8" s="272"/>
+      <c r="G8" s="272"/>
+      <c r="H8" s="273"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="253" t="s">
+      <c r="B9" s="255" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="254"/>
-      <c r="D9" s="258" t="s">
+      <c r="C9" s="256"/>
+      <c r="D9" s="274" t="s">
         <v>226</v>
       </c>
-      <c r="E9" s="259"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="259"/>
-      <c r="H9" s="260"/>
+      <c r="E9" s="275"/>
+      <c r="F9" s="275"/>
+      <c r="G9" s="275"/>
+      <c r="H9" s="276"/>
     </row>
     <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="264" t="s">
+      <c r="B10" s="257" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="265"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="262"/>
-      <c r="F10" s="262"/>
-      <c r="G10" s="262"/>
-      <c r="H10" s="263"/>
+      <c r="C10" s="258"/>
+      <c r="D10" s="277"/>
+      <c r="E10" s="278"/>
+      <c r="F10" s="278"/>
+      <c r="G10" s="278"/>
+      <c r="H10" s="279"/>
     </row>
     <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="12" spans="2:14" ht="14.25" thickBot="1">
@@ -21451,15 +22349,15 @@
         <v>47</v>
       </c>
       <c r="E13" s="106" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="F13" s="47" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
         <v>u4_s_AlertB_grishuSrcchk</v>
       </c>
       <c r="G13" s="47" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
-        <v>vd_s_AlertB_grishuRwTx</v>
+        <f t="shared" ref="G13:G37" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
+        <v>NULL</v>
       </c>
       <c r="H13" s="104" t="str">
         <f ca="1">IF($D13&lt;&gt;"","ALERT_CH_"&amp;UPPER($D$6)&amp;IF($D$7=1,"","_"&amp;UPPER($C13)),"")</f>
@@ -22334,22 +23232,22 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -23798,7 +24696,7 @@
         <v>130</v>
       </c>
       <c r="L4" s="110" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M4" s="47">
         <f ca="1">LEN(N4)</f>
@@ -26584,10 +27482,10 @@
         <v>61</v>
       </c>
       <c r="AH3" s="193" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AI3" s="193" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AJ3" s="283"/>
       <c r="AR3" s="85" t="s">
@@ -27092,7 +27990,7 @@
       </c>
       <c r="AU8" s="58" t="str">
         <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */")</f>
-        <v xml:space="preserve">        &amp;vd_s_AlertB_grishuRwTx,                                               /* fp_vd_XDST                                         */</v>
+        <v xml:space="preserve">        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */</v>
       </c>
       <c r="AV8" s="44" t="s">
         <v>71</v>
@@ -28012,7 +28910,7 @@
       </c>
       <c r="AW15" s="63" t="str">
         <f ca="1">IF(AW6&lt;&gt;AW17,VLOOKUP(AW6,Matrix!$C$13:$G$37,5,FALSE),Matrix!G13)</f>
-        <v>vd_s_AlertB_grishuRwTx</v>
+        <v>NULL</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -55117,10 +56015,11 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -55154,7 +56053,7 @@
   <sheetData>
     <row r="2" spans="2:17" ht="15" thickBot="1">
       <c r="B2" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="15" thickBot="1">
@@ -55280,7 +56179,7 @@
       <c r="O6" s="185"/>
       <c r="P6" s="184"/>
       <c r="Q6" s="194" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="27">
@@ -55298,17 +56197,17 @@
       <c r="I7" s="289"/>
       <c r="J7" s="290"/>
       <c r="K7" s="187" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L7" s="190" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M7" s="28"/>
       <c r="N7" s="184"/>
       <c r="O7" s="185"/>
       <c r="P7" s="184"/>
       <c r="Q7" s="182" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="136.5">
@@ -55340,10 +56239,10 @@
         <v>177</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M8" s="27" t="s">
         <v>29</v>
@@ -55352,7 +56251,7 @@
       <c r="O8" s="185"/>
       <c r="P8" s="184"/>
       <c r="Q8" s="182" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="119.25" customHeight="1" thickBot="1">
@@ -55384,26 +56283,26 @@
         <v>179</v>
       </c>
       <c r="K9" s="202" t="s">
+        <v>243</v>
+      </c>
+      <c r="L9" s="203" t="s">
+        <v>253</v>
+      </c>
+      <c r="M9" s="29" t="s">
         <v>244</v>
-      </c>
-      <c r="L9" s="203" t="s">
-        <v>254</v>
-      </c>
-      <c r="M9" s="29" t="s">
-        <v>245</v>
       </c>
       <c r="N9" s="200"/>
       <c r="O9" s="199" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P9" s="189"/>
       <c r="Q9" s="195" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="14.25" thickTop="1">
       <c r="B10" s="204" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10" s="162" t="s">
         <v>178</v>
@@ -55430,26 +56329,26 @@
         <v>178</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L10" s="33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M10" s="34" t="s">
         <v>225</v>
       </c>
       <c r="N10" s="162"/>
       <c r="O10" s="125" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P10" s="36"/>
       <c r="Q10" s="196" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="205" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C11" s="163" t="s">
         <v>178</v>
@@ -55476,26 +56375,26 @@
         <v>178</v>
       </c>
       <c r="K11" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="L11" s="31" t="s">
         <v>247</v>
-      </c>
-      <c r="L11" s="31" t="s">
-        <v>248</v>
       </c>
       <c r="M11" s="35" t="s">
         <v>232</v>
       </c>
       <c r="N11" s="163"/>
       <c r="O11" s="56" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P11" s="37"/>
       <c r="Q11" s="197" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="205" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C12" s="163" t="s">
         <v>178</v>
@@ -55522,26 +56421,26 @@
         <v>178</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L12" s="31" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M12" s="35" t="s">
         <v>31</v>
       </c>
       <c r="N12" s="163"/>
       <c r="O12" s="56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P12" s="37"/>
       <c r="Q12" s="197" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="2:17">
       <c r="B13" s="205" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C13" s="163" t="s">
         <v>178</v>
@@ -55568,21 +56467,21 @@
         <v>178</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L13" s="31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M13" s="35" t="s">
         <v>31</v>
       </c>
       <c r="N13" s="163"/>
       <c r="O13" s="56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P13" s="37"/>
       <c r="Q13" s="197" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="14.25" thickBot="1">
@@ -55614,26 +56513,26 @@
         <v>178</v>
       </c>
       <c r="K14" s="208" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L14" s="208" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M14" s="209" t="s">
         <v>31</v>
       </c>
       <c r="N14" s="207"/>
       <c r="O14" s="210" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P14" s="211"/>
       <c r="Q14" s="212" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" spans="21:21">
       <c r="U77" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
